--- a/financial/UNLID_財務三表_v4.1.xlsx
+++ b/financial/UNLID_財務三表_v4.1.xlsx
@@ -147,7 +147,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -161,11 +161,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -396,6 +424,8 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1827,9 +1857,9 @@
           <t>※注1：Claude Code等のAPI費用はクライアントが直接負担。UNLIDが負担するのは社内開発・品質管理・FDE業務効率化ツールとしての自社利用分のみ（Claude Pro/Teams等）。</t>
         </is>
       </c>
-      <c r="B74" s="21" t="n"/>
-      <c r="C74" s="21" t="n"/>
-      <c r="D74" s="21" t="n"/>
+      <c r="B74" s="78" t="n"/>
+      <c r="C74" s="78" t="n"/>
+      <c r="D74" s="79" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="22" t="inlineStr">
@@ -2002,10 +2032,10 @@
           <t>【売上高】</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="B4" s="78" t="n"/>
+      <c r="C4" s="78" t="n"/>
+      <c r="D4" s="78" t="n"/>
+      <c r="E4" s="79" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2137,10 +2167,10 @@
           <t>【売上原価（変動費）】</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
+      <c r="B11" s="78" t="n"/>
+      <c r="C11" s="78" t="n"/>
+      <c r="D11" s="78" t="n"/>
+      <c r="E11" s="79" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2271,10 +2301,10 @@
           <t>【販売費及び一般管理費（SGA）】</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n"/>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
+      <c r="B19" s="78" t="n"/>
+      <c r="C19" s="78" t="n"/>
+      <c r="D19" s="78" t="n"/>
+      <c r="E19" s="79" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2664,10 +2694,10 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr"/>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="21" t="n"/>
+      <c r="B38" s="78" t="n"/>
+      <c r="C38" s="78" t="n"/>
+      <c r="D38" s="78" t="n"/>
+      <c r="E38" s="79" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="36" t="inlineStr">
@@ -2859,10 +2889,10 @@
           <t>【資産の部】</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="B4" s="78" t="n"/>
+      <c r="C4" s="78" t="n"/>
+      <c r="D4" s="78" t="n"/>
+      <c r="E4" s="79" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -3008,10 +3038,10 @@
           <t>【負債の部】</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
+      <c r="B12" s="78" t="n"/>
+      <c r="C12" s="78" t="n"/>
+      <c r="D12" s="78" t="n"/>
+      <c r="E12" s="79" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -3138,10 +3168,10 @@
           <t>【純資産の部】</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n"/>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
+      <c r="B19" s="78" t="n"/>
+      <c r="C19" s="78" t="n"/>
+      <c r="D19" s="78" t="n"/>
+      <c r="E19" s="79" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -3333,10 +3363,10 @@
           <t>【営業活動によるCF】（間接法）</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="B4" s="78" t="n"/>
+      <c r="C4" s="78" t="n"/>
+      <c r="D4" s="78" t="n"/>
+      <c r="E4" s="79" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -3512,10 +3542,10 @@
           <t>【投資活動によるCF】</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
+      <c r="B13" s="78" t="n"/>
+      <c r="C13" s="78" t="n"/>
+      <c r="D13" s="78" t="n"/>
+      <c r="E13" s="79" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -3576,10 +3606,10 @@
           <t>【財務活動によるCF】</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
+      <c r="B17" s="78" t="n"/>
+      <c r="C17" s="78" t="n"/>
+      <c r="D17" s="78" t="n"/>
+      <c r="E17" s="79" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -3698,10 +3728,10 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="21" t="n"/>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
+      <c r="B23" s="78" t="n"/>
+      <c r="C23" s="78" t="n"/>
+      <c r="D23" s="78" t="n"/>
+      <c r="E23" s="79" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -4683,14 +4713,14 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>【分析④】FDE雇用形態別ユニットエコノミクス（1FDE×6社掛け持ち）</t>
+          <t>【分析④】FDE雇用形態別ユニットエコノミクス（1FDE×5社担当）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>FDE1名が6社（各月20万円）を担当した場合の粗利・採用費回収試算</t>
+          <t>FDE1名が5社（各月24万円）を担当した場合の粗利・採用費回収試算</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4737,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>月商(6社)</t>
+          <t>月商(5社)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -4812,11 +4842,11 @@
       </c>
       <c r="B55" s="36" t="inlineStr">
         <is>
-          <t>業務委託（単価23万）</t>
+          <t>業務委託（単価25万）</t>
         </is>
       </c>
       <c r="C55" s="55" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D55" s="55" t="n">
         <v>25</v>

--- a/financial/UNLID_財務三表_v4.1.xlsx
+++ b/financial/UNLID_財務三表_v4.1.xlsx
@@ -4713,14 +4713,14 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>【分析④】FDE雇用形態別ユニットエコノミクス（1FDE×5社担当）</t>
+          <t>【分析④】FDE雇用形態別ユニットエコノミクス（1FDE×6社掛け持ち）</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>FDE1名が5社（各月24万円）を担当した場合の粗利・採用費回収試算</t>
+          <t>FDE1名が6社（各月20万円）を担当した場合の粗利・採用費回収試算</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>月商(5社)</t>
+          <t>月商(6社)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -4842,11 +4842,11 @@
       </c>
       <c r="B55" s="36" t="inlineStr">
         <is>
-          <t>業務委託（単価25万）</t>
+          <t>業務委託（単価23万）</t>
         </is>
       </c>
       <c r="C55" s="55" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D55" s="55" t="n">
         <v>25</v>
